--- a/data/merged/2026-09-09/MERGED_ES_Spot-Cleaner_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_ES_Spot-Cleaner_2026-09-09.xlsx
@@ -7013,50 +7013,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7382,7 +7338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16757,40 +16713,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0DDPL3PD2</t>
+          <t>B0CZCVCM65</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>EUREKA</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Vacmaster/page/935EC746-F3AD-4C28-9B32-85256EBEE494?lp_asin=B0DDPL3PD2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/EUREKA/page/F2939BAC-A9D5-40E4-9C75-132C2F8585BD?lp_asin=B0CZCVCM65&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Clean &amp; Restore Carpet Cleaner Formula – CCS04</t>
+          <t>Eureka NEY100 Aspirador Tapicerias con Agua, Aspiradora de Agua con Solución, Maquina Limpiador para Limpiar Tapicerias, Alfo</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DDPL3PD2?psc=1</t>
+          <t>https://www.amazon.es/dp/B0CZCVCM65?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/414atrxj5NL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0DDPL3PD2</t>
+          <t>B0CZCVCM65</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16804,13 +16760,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>7433</v>
+        <v>49337</v>
       </c>
       <c r="P42" s="15">
-        <v>-591</v>
+        <v>-20477</v>
       </c>
       <c r="Q42" s="16">
-        <v>-0.09</v>
+        <v>-0.71</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16819,75 +16775,69 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>181</v>
+        <v>46</v>
       </c>
       <c r="U42" s="16">
-        <v>0.12</v>
+        <v>-0.66</v>
       </c>
       <c r="V42" s="15">
-        <v>3618</v>
-      </c>
-      <c r="W42" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X42" s="15">
-        <v>1999</v>
-      </c>
+        <v>3365</v>
+      </c>
+      <c r="W42" s="15"/>
+      <c r="X42" s="15"/>
       <c r="Y42" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="20">
-        <v>19.99</v>
+        <v>73.16</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="19">
-        <v>647</v>
+        <v>1430</v>
       </c>
       <c r="AE42" s="15">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.2376</v>
+        <v>0.21739999999999998</v>
       </c>
       <c r="AH42" s="20">
-        <v>5.58</v>
+        <v>7.03</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>746</v>
+        <v>879</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
       <c r="AO42" s="13"/>
       <c r="AP42"/>
       <c r="AQ42" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
@@ -16896,7 +16846,7 @@
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU42" s="13"/>
@@ -16916,7 +16866,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD42" s="13"/>
+      <c r="BD42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE42" s="13"/>
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
@@ -16928,47 +16882,47 @@
       </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>2,03 kg</t>
+          <t>4,7 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>4.70 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>25 x 16,8 x 7,6 cm</t>
+          <t>19,5 x 38,5 x 30 cm</t>
         </is>
       </c>
       <c r="BM42" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 16.80 x 7.60 cm</t>
+          <t>19.50 x 38.50 x 30.00 cm</t>
         </is>
       </c>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>5.48 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>5.48 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>25 x 16.8 x 7.6 cm</t>
+          <t>44.5 x 34.1 x 20 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 16.80 x 7.60 cm</t>
+          <t>44.50 x 34.10 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16979,40 +16933,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0CZCVCM65</t>
+          <t>B0H7C5V7MZ</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>EUREKA</t>
+          <t>VacniQ</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/EUREKA/page/F2939BAC-A9D5-40E4-9C75-132C2F8585BD?lp_asin=B0CZCVCM65&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/Buenaelecci%C3%B3nparaaspiradora/page/B8B0FA9F-58B0-4E3B-92F7-73B72A16FBF1?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Eureka NEY100 Aspirador Tapicerias con Agua, Aspiradora de Agua con Solución, Maquina Limpiador para Limpiar Tapicerias, Alfo</t>
+          <t>VacniQ C688 aspiradora limpiadora 4 en 1, 25000 Pa, 1800 W. Calefacción, desinfección, pantalla LED y avisos vocales. Ideal p</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0CZCVCM65?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H7C5V7MZ?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/414atrxj5NL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71NNLpx5enL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0CZCVCM65</t>
+          <t>B0H7C5V7MZ</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17026,13 +16980,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>49337</v>
+        <v>13153</v>
       </c>
       <c r="P43" s="15">
-        <v>-20477</v>
+        <v>27887</v>
       </c>
       <c r="Q43" s="16">
-        <v>-0.71</v>
+        <v>0.68</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17041,89 +16995,93 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>46</v>
-      </c>
-      <c r="U43" s="16">
-        <v>-0.66</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="U43" s="16"/>
       <c r="V43" s="15">
-        <v>3365</v>
+        <v>2520</v>
       </c>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
       <c r="Y43" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>73.16</v>
+        <v>139.99</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="19">
-        <v>1430</v>
+        <v>7</v>
       </c>
       <c r="AE43" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.21739999999999998</v>
+        <v>0.3333</v>
       </c>
       <c r="AH43" s="20">
-        <v>7.03</v>
+        <v>7.35</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>879</v>
+        <v>67</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43"/>
-      <c r="AQ43" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ43" s="19"/>
       <c r="AR43" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Guevel David Commerce</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU43" s="13"/>
-      <c r="AV43" s="14"/>
-      <c r="AW43" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU43" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV43" s="14" t="inlineStr">
+        <is>
+          <t>Paris 75002 FR</t>
+        </is>
+      </c>
+      <c r="AW43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E</t>
+        </is>
+      </c>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY43" s="13"/>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
@@ -17132,63 +17090,47 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD43" s="13"/>
       <c r="BE43" s="13"/>
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
-      <c r="BI43" t="inlineStr">
-        <is>
-          <t>Opción Amazon</t>
-        </is>
-      </c>
+      <c r="BI43"/>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>4,7 kg</t>
+          <t>6 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>4.70 kg</t>
-        </is>
-      </c>
-      <c r="BL43" s="23" t="inlineStr">
-        <is>
-          <t>19,5 x 38,5 x 30 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="23" t="inlineStr">
-        <is>
-          <t>19.50 x 38.50 x 30.00 cm</t>
-        </is>
-      </c>
+          <t>6.00 kg</t>
+        </is>
+      </c>
+      <c r="BL43" s="23"/>
+      <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>5.48 kg</t>
+          <t>6 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>5.48 kg</t>
+          <t>6.00 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>44.5 x 34.1 x 20 cm</t>
+          <t>44 x 32 x 26 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>44.50 x 34.10 x 20.00 cm</t>
+          <t>44.00 x 32.00 x 26.00 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17199,40 +17141,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0H7C5V7MZ</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>VacniQ</t>
+          <t>Redkey</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Buenaelecci%C3%B3nparaaspiradora/page/B8B0FA9F-58B0-4E3B-92F7-73B72A16FBF1?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.es/Redkey/b/ref=bl_dp_s_web_88917816031?ie=UTF8&amp;node=88917816031&amp;field-lbr_brands_browse-bin=Redkey</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>VacniQ C688 aspiradora limpiadora 4 en 1, 25000 Pa, 1800 W. Calefacción, desinfección, pantalla LED y avisos vocales. Ideal p</t>
+          <t>Redkey Rd-F1 Aspirador Tapicerías con Agua, 4 en 1 Aspirador Lava a Vapor con Succión 26000Pa, 1800W Limpieza Profunda para A</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H7C5V7MZ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H4TXR27S?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71NNLpx5enL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0H7C5V7MZ</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17246,13 +17188,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>13153</v>
+        <v>12011</v>
       </c>
       <c r="P44" s="15">
-        <v>27887</v>
+        <v>151301</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.68</v>
+        <v>0.93</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17261,15 +17203,15 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U44" s="16"/>
       <c r="V44" s="15">
-        <v>2520</v>
+        <v>1960</v>
       </c>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
@@ -17282,70 +17224,54 @@
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="15"/>
-      <c r="AD44" s="19">
-        <v>7</v>
-      </c>
-      <c r="AE44" s="15">
-        <v>6</v>
-      </c>
-      <c r="AF44" s="21">
-        <v>5</v>
-      </c>
+      <c r="AD44" s="19"/>
+      <c r="AE44" s="15"/>
+      <c r="AF44" s="21"/>
       <c r="AG44" s="22">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="AH44" s="20">
-        <v>7.35</v>
+        <v>9.75</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44"/>
-      <c r="AQ44" s="19"/>
+      <c r="AQ44" s="19">
+        <v>8</v>
+      </c>
       <c r="AR44" s="19">
         <v>1</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Guevel David Commerce</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="AV44" s="14" t="inlineStr">
-        <is>
-          <t>Paris 75002 FR</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU44" s="13"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="13"/>
       <c r="AX44" s="13"/>
       <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
@@ -17364,39 +17290,39 @@
       <c r="BI44"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>6 kg</t>
+          <t>6,8 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>6.00 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BL44" s="23"/>
       <c r="BM44" s="23"/>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>6 kg</t>
+          <t>6.8 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>6.00 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>44 x 32 x 26 cm</t>
+          <t>37 x 35 x 35 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 32.00 x 26.00 cm</t>
+          <t>37.00 x 35.00 x 35.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17407,40 +17333,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
+          <t>B0CVXFZR27</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Redkey</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/Redkey/b/ref=bl_dp_s_web_88917816031?ie=UTF8&amp;node=88917816031&amp;field-lbr_brands_browse-bin=Redkey</t>
+          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0CVXFZR27&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Redkey Rd-F1 Aspirador Tapicerías con Agua, 4 en 1 Aspirador Lava a Vapor con Succión 26000Pa, 1800W Limpieza Profunda para A</t>
+          <t>HAUSHOF StainZapper Air Aspiradora de Agua Inalámbrica 24VsLimpiador de Tapicerías sin Cable para Sofás, Moquetas y Asiento</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H4TXR27S?psc=1</t>
+          <t>https://www.amazon.es/dp/B0CVXFZR27?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71oWuvgi1DL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
+          <t>B0CVXFZR27</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17454,13 +17380,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>12011</v>
+        <v>68444</v>
       </c>
       <c r="P45" s="15">
-        <v>151301</v>
+        <v>93278</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.93</v>
+        <v>0.58</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17469,15 +17395,17 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>14</v>
-      </c>
-      <c r="U45" s="16"/>
+        <v>19</v>
+      </c>
+      <c r="U45" s="16">
+        <v>3</v>
+      </c>
       <c r="V45" s="15">
-        <v>1960</v>
+        <v>1900</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
@@ -17485,19 +17413,25 @@
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>139.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="15"/>
-      <c r="AD45" s="19"/>
-      <c r="AE45" s="15"/>
-      <c r="AF45" s="21"/>
+      <c r="AD45" s="19">
+        <v>165</v>
+      </c>
+      <c r="AE45" s="15">
+        <v>4</v>
+      </c>
+      <c r="AF45" s="21">
+        <v>4</v>
+      </c>
       <c r="AG45" s="22">
-        <v>0</v>
+        <v>0.21050000000000002</v>
       </c>
       <c r="AH45" s="20">
-        <v>9.75</v>
+        <v>7.45</v>
       </c>
       <c r="AI45" s="16">
         <v>0.78</v>
@@ -17505,39 +17439,51 @@
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>19</v>
+        <v>764</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45"/>
       <c r="AQ45" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR45" s="19">
         <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>GreatStarTools</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU45" s="13"/>
-      <c r="AV45" s="14"/>
-      <c r="AW45" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU45" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV45" s="14" t="inlineStr">
+        <is>
+          <t>Shangcheng Zhejiang 310019 CN</t>
+        </is>
+      </c>
+      <c r="AW45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC</t>
+        </is>
+      </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
@@ -17548,7 +17494,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13"/>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
@@ -17556,39 +17506,47 @@
       <c r="BI45"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>6,8 kg</t>
+          <t>5,36 kg</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
-        </is>
-      </c>
-      <c r="BL45" s="23"/>
-      <c r="BM45" s="23"/>
+          <t>5.36 kg</t>
+        </is>
+      </c>
+      <c r="BL45" s="23" t="inlineStr">
+        <is>
+          <t>20 x 38 x 30 cm</t>
+        </is>
+      </c>
+      <c r="BM45" s="23" t="inlineStr">
+        <is>
+          <t>20.00 x 38.00 x 30.00 cm</t>
+        </is>
+      </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>6.8 kg</t>
+          <t>5.36 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
+          <t>5.36 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>37 x 35 x 35 cm</t>
+          <t>44.5 x 34 x 20 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>37.00 x 35.00 x 35.00 cm</t>
+          <t>44.50 x 34.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17599,45 +17557,45 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0CVXFZR27</t>
+          <t>B0DSC939TV</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>CLEANmaxx</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0CVXFZR27&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Air Aspiradora de Agua Inalámbrica 24VsLimpiador de Tapicerías sin Cable para Sofás, Moquetas y Asiento</t>
+          <t>CLEANmaxx Limpiador de tapicería Pro de 400 W, potente aspiradora de lavado con función de autolimpieza y 2 boquillas, ideal</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0CVXFZR27?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DSC939TV?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71oWuvgi1DL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41S5-Tk+PjL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0CVXFZR27</t>
+          <t>B0DSC939TV</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
+          <t>Bricolaje y herramientas:Herramientas manuales y eléctricas:Herramientas eléctricas:Aspiradoras industriales para sólidos y líquidos</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
@@ -17646,125 +17604,107 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>68444</v>
+        <v>19358</v>
       </c>
       <c r="P46" s="15">
-        <v>93278</v>
+        <v>72629</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
-          <t>Aspiradoras para alfombras</t>
+          <t>Aspiradoras para alfombras
+Aspiradoras industriales para sólidos y líquidos</t>
         </is>
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>38
+233</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U46" s="16">
-        <v>3</v>
+        <v>4.67</v>
       </c>
       <c r="V46" s="15">
-        <v>1900</v>
+        <v>1490</v>
       </c>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z46" s="20">
-        <v>99.99</v>
+        <v>74.49</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="19">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="AE46" s="15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="21">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.21050000000000002</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="20">
-        <v>7.45</v>
+        <v>9.06</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>764</v>
+        <v>608</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR46" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>GreatStarTools</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU46" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV46" s="14" t="inlineStr">
-        <is>
-          <t>Shangcheng Zhejiang 310019 CN</t>
-        </is>
-      </c>
-      <c r="AW46" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU46" s="13"/>
+      <c r="AV46" s="14"/>
+      <c r="AW46" s="13"/>
       <c r="AX46" s="13"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC46" s="13"/>
+      <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
@@ -17772,47 +17712,43 @@
       <c r="BI46"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>5,36 kg</t>
+          <t>4 Kilogramos</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>5.36 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>20 x 38 x 30 cm</t>
-        </is>
-      </c>
-      <c r="BM46" s="23" t="inlineStr">
-        <is>
-          <t>20.00 x 38.00 x 30.00 cm</t>
-        </is>
-      </c>
+          <t>33,5f. x 29,5an. x 33al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM46" s="23"/>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>5.36 kg</t>
+          <t>4.52 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>5.36 kg</t>
+          <t>4.52 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>44.5 x 34 x 20 cm</t>
+          <t>36.9 x 34.5 x 28.5 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>44.50 x 34.00 x 20.00 cm</t>
+          <t>36.90 x 34.50 x 28.50 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17823,45 +17759,45 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0DSC939TV</t>
+          <t>B0CWV3BTDZ</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx</t>
+          <t>Kamanan</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx</t>
+          <t>https://www.amazon.es/Kamanan/b/ref=bl_dp_s_web_66105826031?ie=UTF8&amp;node=66105826031&amp;field-lbr_brands_browse-bin=Kamanan</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx Limpiador de tapicería Pro de 400 W, potente aspiradora de lavado con función de autolimpieza y 2 boquillas, ideal</t>
+          <t>Kamanan Aspirador de ácaros de 100 W, para colchones, antiácaros, aspiradora con luz UV y depósito Permanente para colchones,</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DSC939TV?psc=1</t>
+          <t>https://www.amazon.es/dp/B0CWV3BTDZ?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41S5-Tk+PjL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61MdLxg7mKL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0DSC939TV</t>
+          <t>B0CWV3BTDZ</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
-          <t>Bricolaje y herramientas:Herramientas manuales y eléctricas:Herramientas eléctricas:Aspiradoras industriales para sólidos y líquidos</t>
+          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
         </is>
       </c>
       <c r="N47" s="14" t="inlineStr">
@@ -17870,151 +17806,177 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>19358</v>
+        <v>139919</v>
       </c>
       <c r="P47" s="15">
-        <v>72629</v>
+        <v>-91999</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.79</v>
+        <v>-1.92</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
-          <t>Aspiradoras para alfombras
-Aspiradoras industriales para sólidos y líquidos</t>
+          <t>Aspiradoras para alfombras</t>
         </is>
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>38
-233</t>
+          <t>59</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="U47" s="16">
-        <v>4.67</v>
+        <v>-0.64</v>
       </c>
       <c r="V47" s="15">
-        <v>1490</v>
+        <v>1363</v>
       </c>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
       <c r="Y47" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z47" s="20">
-        <v>74.49</v>
+        <v>49.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="19">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="AE47" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG47" s="22">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="AH47" s="20">
-        <v>9.06</v>
+        <v>5.15</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>608</v>
+        <v>858</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
       <c r="AQ47" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR47" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>radishde</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU47" s="13"/>
-      <c r="AV47" s="14"/>
-      <c r="AW47" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU47" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV47" s="14" t="inlineStr">
+        <is>
+          <t>DunKouXiaoQu WuHanShi 430100 CN</t>
+        </is>
+      </c>
+      <c r="AW47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UMTMFY4BME13</t>
+        </is>
+      </c>
       <c r="AX47" s="13"/>
-      <c r="AY47" s="13"/>
+      <c r="AY47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
-      <c r="BC47" s="13"/>
+      <c r="BC47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD47" s="13"/>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47"/>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>Opción Amazon</t>
+        </is>
+      </c>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>4 Kilogramos</t>
+          <t>1,24 Kilogramos</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>33,5f. x 29,5an. x 33al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM47" s="23"/>
+          <t>25 x 25 x 12 cm</t>
+        </is>
+      </c>
+      <c r="BM47" s="23" t="inlineStr">
+        <is>
+          <t>25.00 x 25.00 x 12.00 cm</t>
+        </is>
+      </c>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>4.52 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>4.52 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>36.9 x 34.5 x 28.5 cm</t>
+          <t>28 x 27.8 x 18.1 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>36.90 x 34.50 x 28.50 cm</t>
+          <t>28.00 x 27.80 x 18.10 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -18025,40 +17987,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0CWV3BTDZ</t>
+          <t>B0GL6L64YM</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Kamanan</t>
+          <t>WORKPRO</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/Kamanan/b/ref=bl_dp_s_web_66105826031?ie=UTF8&amp;node=66105826031&amp;field-lbr_brands_browse-bin=Kamanan</t>
+          <t>https://www.amazon.es/stores/WORKPRO/page/BDAC63AC-F4AC-4F79-BFBC-4C0D40DF1554?lp_asin=B0GL6L64YM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Kamanan Aspirador de ácaros de 100 W, para colchones, antiácaros, aspiradora con luz UV y depósito Permanente para colchones,</t>
+          <t>WORKPRO Limpiador de Tapicerías y Alfombras a Vapor con Aspirador 4 en 1, Potente Succión 16 kPa, Accesorios para Suciedad de</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0CWV3BTDZ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GL6L64YM?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61MdLxg7mKL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41P+iDWNq4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0CWV3BTDZ</t>
+          <t>B0GL6L64YM</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18072,13 +18034,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>139919</v>
+        <v>93545</v>
       </c>
       <c r="P48" s="15">
-        <v>-91999</v>
+        <v>249961</v>
       </c>
       <c r="Q48" s="16">
-        <v>-1.92</v>
+        <v>0.86</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18087,17 +18049,17 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="U48" s="16">
-        <v>-0.64</v>
+        <v>-0.24</v>
       </c>
       <c r="V48" s="15">
-        <v>1363</v>
+        <v>1260</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
@@ -18105,37 +18067,37 @@
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>49.99</v>
+        <v>139.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="19">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="AE48" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF48" s="21">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0345</v>
+        <v>0.44439999999999996</v>
       </c>
       <c r="AH48" s="20">
-        <v>5.15</v>
+        <v>9.06</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>858</v>
+        <v>106</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -18153,7 +18115,7 @@
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>radishde</t>
+          <t>GreatStarTools</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
@@ -18168,20 +18130,16 @@
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>DunKouXiaoQu WuHanShi 430100 CN</t>
+          <t>Shangcheng Zhejiang 310019 CN</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UMTMFY4BME13</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
@@ -18195,54 +18153,50 @@
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" t="inlineStr">
-        <is>
-          <t>Opción Amazon</t>
-        </is>
-      </c>
+      <c r="BI48"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>1,24 Kilogramos</t>
+          <t>7,32 kg</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>7.32 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>25 x 25 x 12 cm</t>
+          <t>23 x 34 x 28 cm</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 25.00 x 12.00 cm</t>
+          <t>23.00 x 34.00 x 28.00 cm</t>
         </is>
       </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>7.32 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>7.32 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>28 x 27.8 x 18.1 cm</t>
+          <t>38 x 37.6 x 26.5 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>28.00 x 27.80 x 18.10 cm</t>
+          <t>38.00 x 37.60 x 26.50 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18253,40 +18207,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0GL6L64YM</t>
+          <t>B0HF7YZWZZ</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>WORKPRO</t>
+          <t>Kiseely</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/WORKPRO/page/BDAC63AC-F4AC-4F79-BFBC-4C0D40DF1554?lp_asin=B0GL6L64YM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kiseely</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>WORKPRO Limpiador de Tapicerías y Alfombras a Vapor con Aspirador 4 en 1, Potente Succión 16 kPa, Accesorios para Suciedad de</t>
+          <t>Aspiradora Agua Tapiceria Limpiador, con calentamiento instantáneo, 600W potente succión y limpieza profunda para alfombras,</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GL6L64YM?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HF7YZWZZ?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41P+iDWNq4L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41jxwo0ip7L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0GL6L64YM</t>
+          <t>B0HF7YZWZZ</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18300,13 +18254,13 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>93545</v>
+        <v>55804</v>
       </c>
       <c r="P49" s="15">
-        <v>249961</v>
+        <v>-79275</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.86</v>
+        <v>-1.03</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -18315,43 +18269,41 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>9</v>
-      </c>
-      <c r="U49" s="16">
-        <v>-0.24</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="U49" s="16"/>
       <c r="V49" s="15">
-        <v>1260</v>
+        <v>900</v>
       </c>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
       <c r="Y49" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="20">
-        <v>139.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AE49" s="15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF49" s="21">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.44439999999999996</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="20">
-        <v>9.06</v>
+        <v>5.05</v>
       </c>
       <c r="AI49" s="16">
         <v>0.79</v>
@@ -18359,11 +18311,11 @@
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -18373,15 +18325,13 @@
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
-      <c r="AQ49" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ49" s="19"/>
       <c r="AR49" s="19">
         <v>1</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>GreatStarTools</t>
+          <t>Fly around wholesale</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -18396,12 +18346,12 @@
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>Shangcheng Zhejiang 310019 CN</t>
+          <t>广州市 天河区 广东省 510630 CN</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31A3I5NU1NCR2</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -18409,11 +18359,7 @@
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="13"/>
       <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
@@ -18422,47 +18368,39 @@
       <c r="BI49"/>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>7,32 kg</t>
+          <t>2,5 kg</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>7.32 kg</t>
-        </is>
-      </c>
-      <c r="BL49" s="23" t="inlineStr">
-        <is>
-          <t>23 x 34 x 28 cm</t>
-        </is>
-      </c>
-      <c r="BM49" s="23" t="inlineStr">
-        <is>
-          <t>23.00 x 34.00 x 28.00 cm</t>
-        </is>
-      </c>
+          <t>2.50 kg</t>
+        </is>
+      </c>
+      <c r="BL49" s="23"/>
+      <c r="BM49" s="23"/>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>7.32 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>7.32 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>38 x 37.6 x 26.5 cm</t>
+          <t>30 x 20 x 15 cm</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>38.00 x 37.60 x 26.50 cm</t>
+          <t>30.00 x 20.00 x 15.00 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -18473,153 +18411,83 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0HF7YZWZZ</t>
+          <t>B0FNRQFHWC</t>
         </is>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>Kiseely</t>
-        </is>
-      </c>
+      <c r="F50" s="14"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kiseely</t>
+          <t>https://www.amazon.esundefined</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora Agua Tapiceria Limpiador, con calentamiento instantáneo, 600W potente succión y limpieza profunda para alfombras,</t>
+          <t>Shark StainForce, Eliminación de manchas y olores en alfombras, moquetas, tapicería, escaleras y coches, diseño ligero y port</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0HF7YZWZZ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FNRQFHWC?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41jxwo0ip7L._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0HF7YZWZZ</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>55804</v>
-      </c>
-      <c r="P50" s="15">
-        <v>-79275</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>-1.03</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>10</v>
-      </c>
+          <t>B0FNRQFHWC</t>
+        </is>
+      </c>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="15"/>
       <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>900</v>
-      </c>
+      <c r="V50" s="15"/>
       <c r="W50" s="15"/>
       <c r="X50" s="15"/>
-      <c r="Y50" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>89.99</v>
-      </c>
+      <c r="Y50" s="19"/>
+      <c r="Z50" s="20"/>
       <c r="AA50"/>
       <c r="AB50"/>
       <c r="AC50" s="15"/>
       <c r="AD50" s="19">
-        <v>7</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AE50" s="15"/>
       <c r="AF50" s="21">
         <v>5</v>
       </c>
       <c r="AG50" s="22">
         <v>0</v>
       </c>
-      <c r="AH50" s="20">
-        <v>5.05</v>
-      </c>
+      <c r="AH50" s="20"/>
       <c r="AI50" s="16">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>24</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK50" s="13"/>
+      <c r="AL50" s="19"/>
+      <c r="AM50" s="13"/>
       <c r="AN50" s="13"/>
       <c r="AO50" s="13"/>
       <c r="AP50"/>
       <c r="AQ50" s="19"/>
-      <c r="AR50" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>Fly around wholesale</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>广州市 天河区 广东省 510630 CN</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31A3I5NU1NCR2</t>
-        </is>
-      </c>
+      <c r="AR50" s="19"/>
+      <c r="AS50" s="14"/>
+      <c r="AT50" s="13"/>
+      <c r="AU50" s="13"/>
+      <c r="AV50" s="14"/>
+      <c r="AW50" s="13"/>
       <c r="AX50" s="13"/>
       <c r="AY50" s="13"/>
       <c r="AZ50" s="13"/>
@@ -18632,149 +18500,15 @@
       <c r="BG50" s="13"/>
       <c r="BH50" s="14"/>
       <c r="BI50"/>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>2,5 kg</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
+      <c r="BJ50" s="23"/>
+      <c r="BK50" s="23"/>
       <c r="BL50" s="23"/>
       <c r="BM50" s="23"/>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>2.5 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>30 x 20 x 15 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>30.00 x 20.00 x 15.00 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0FNRQFHWC</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.esundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Shark StainForce, Eliminación de manchas y olores en alfombras, moquetas, tapicería, escaleras y coches, diseño ligero y port</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0FNRQFHWC?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0FNRQFHWC</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>4</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
+      <c r="BN50" s="23"/>
+      <c r="BO50" s="23"/>
+      <c r="BP50" s="23"/>
+      <c r="BQ50" s="23"/>
+      <c r="BR50" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19073,81 +18807,74 @@
     <hyperlink ref="L41" r:id="rId291" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
     <hyperlink ref="M41" r:id="rId292" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N41" r:id="rId293"/>
-    <hyperlink ref="C42" r:id="rId294" tooltip="https://www.amazon.es/dp/B0DDPL3PD2"/>
-    <hyperlink ref="G42" r:id="rId295" tooltip="https://www.amazon.es/stores/Vacmaster/page/935EC746-F3AD-4C28-9B32-85256EBEE494?lp_asin=B0DDPL3PD2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId296" tooltip="https://www.amazon.es/dp/B0DDPL3PD2?psc=1"/>
-    <hyperlink ref="K42" r:id="rId297" tooltip="https://images-na.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId298" tooltip="https://www.amazon.es/dp/B0DDPL3PD2"/>
+    <hyperlink ref="C42" r:id="rId294" tooltip="https://www.amazon.es/dp/B0CZCVCM65"/>
+    <hyperlink ref="G42" r:id="rId295" tooltip="https://www.amazon.es/stores/EUREKA/page/F2939BAC-A9D5-40E4-9C75-132C2F8585BD?lp_asin=B0CZCVCM65&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J42" r:id="rId296" tooltip="https://www.amazon.es/dp/B0CZCVCM65?psc=1"/>
+    <hyperlink ref="K42" r:id="rId297" tooltip="https://m.media-amazon.com/images/I/414atrxj5NL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId298" tooltip="https://www.amazon.es/dp/B0CZCVCM65"/>
     <hyperlink ref="M42" r:id="rId299" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N42" r:id="rId300"/>
-    <hyperlink ref="C43" r:id="rId301" tooltip="https://www.amazon.es/dp/B0CZCVCM65"/>
-    <hyperlink ref="G43" r:id="rId302" tooltip="https://www.amazon.es/stores/EUREKA/page/F2939BAC-A9D5-40E4-9C75-132C2F8585BD?lp_asin=B0CZCVCM65&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId303" tooltip="https://www.amazon.es/dp/B0CZCVCM65?psc=1"/>
-    <hyperlink ref="K43" r:id="rId304" tooltip="https://m.media-amazon.com/images/I/414atrxj5NL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId305" tooltip="https://www.amazon.es/dp/B0CZCVCM65"/>
+    <hyperlink ref="C43" r:id="rId301" tooltip="https://www.amazon.es/dp/B0H7C5V7MZ"/>
+    <hyperlink ref="G43" r:id="rId302" tooltip="https://www.amazon.es/stores/Buenaelecci%C3%B3nparaaspiradora/page/B8B0FA9F-58B0-4E3B-92F7-73B72A16FBF1?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln"/>
+    <hyperlink ref="J43" r:id="rId303" tooltip="https://www.amazon.es/dp/B0H7C5V7MZ?psc=1"/>
+    <hyperlink ref="K43" r:id="rId304" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NNLpx5enL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId305" tooltip="https://www.amazon.es/dp/B0H7C5V7MZ"/>
     <hyperlink ref="M43" r:id="rId306" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N43" r:id="rId307"/>
-    <hyperlink ref="C44" r:id="rId308" tooltip="https://www.amazon.es/dp/B0H7C5V7MZ"/>
-    <hyperlink ref="G44" r:id="rId309" tooltip="https://www.amazon.es/stores/Buenaelecci%C3%B3nparaaspiradora/page/B8B0FA9F-58B0-4E3B-92F7-73B72A16FBF1?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln"/>
-    <hyperlink ref="J44" r:id="rId310" tooltip="https://www.amazon.es/dp/B0H7C5V7MZ?psc=1"/>
-    <hyperlink ref="K44" r:id="rId311" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NNLpx5enL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId312" tooltip="https://www.amazon.es/dp/B0H7C5V7MZ"/>
-    <hyperlink ref="M44" r:id="rId313" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N44" r:id="rId314"/>
-    <hyperlink ref="AW44" r:id="rId315" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
-    <hyperlink ref="C45" r:id="rId316" tooltip="https://www.amazon.es/dp/B0H4TXR27S"/>
-    <hyperlink ref="G45" r:id="rId317" tooltip="https://www.amazon.es/Redkey/b/ref=bl_dp_s_web_88917816031?ie=UTF8&amp;node=88917816031&amp;field-lbr_brands_browse-bin=Redkey"/>
-    <hyperlink ref="J45" r:id="rId318" tooltip="https://www.amazon.es/dp/B0H4TXR27S?psc=1"/>
-    <hyperlink ref="K45" r:id="rId319" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId320" tooltip="https://www.amazon.es/dp/B0H4TXR27S"/>
+    <hyperlink ref="AW43" r:id="rId308" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
+    <hyperlink ref="C44" r:id="rId309" tooltip="https://www.amazon.es/dp/B0H4TXR27S"/>
+    <hyperlink ref="G44" r:id="rId310" tooltip="https://www.amazon.es/Redkey/b/ref=bl_dp_s_web_88917816031?ie=UTF8&amp;node=88917816031&amp;field-lbr_brands_browse-bin=Redkey"/>
+    <hyperlink ref="J44" r:id="rId311" tooltip="https://www.amazon.es/dp/B0H4TXR27S?psc=1"/>
+    <hyperlink ref="K44" r:id="rId312" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId313" tooltip="https://www.amazon.es/dp/B0H4TXR27S"/>
+    <hyperlink ref="M44" r:id="rId314" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N44" r:id="rId315"/>
+    <hyperlink ref="C45" r:id="rId316" tooltip="https://www.amazon.es/dp/B0CVXFZR27"/>
+    <hyperlink ref="G45" r:id="rId317" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0CVXFZR27&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId318" tooltip="https://www.amazon.es/dp/B0CVXFZR27?psc=1"/>
+    <hyperlink ref="K45" r:id="rId319" tooltip="https://images-na.ssl-images-amazon.com/images/I/71oWuvgi1DL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId320" tooltip="https://www.amazon.es/dp/B0CVXFZR27"/>
     <hyperlink ref="M45" r:id="rId321" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N45" r:id="rId322"/>
-    <hyperlink ref="C46" r:id="rId323" tooltip="https://www.amazon.es/dp/B0CVXFZR27"/>
-    <hyperlink ref="G46" r:id="rId324" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0CVXFZR27&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId325" tooltip="https://www.amazon.es/dp/B0CVXFZR27?psc=1"/>
-    <hyperlink ref="K46" r:id="rId326" tooltip="https://images-na.ssl-images-amazon.com/images/I/71oWuvgi1DL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId327" tooltip="https://www.amazon.es/dp/B0CVXFZR27"/>
-    <hyperlink ref="M46" r:id="rId328" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N46" r:id="rId329"/>
-    <hyperlink ref="AW46" r:id="rId330" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC"/>
-    <hyperlink ref="C47" r:id="rId331" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
-    <hyperlink ref="G47" r:id="rId332" tooltip="https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx"/>
-    <hyperlink ref="J47" r:id="rId333" tooltip="https://www.amazon.es/dp/B0DSC939TV?psc=1"/>
-    <hyperlink ref="K47" r:id="rId334" tooltip="https://m.media-amazon.com/images/I/41S5-Tk+PjL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId335" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
-    <hyperlink ref="M47" r:id="rId336" tooltip="https://www.amazon.es/b?node=2165709031"/>
+    <hyperlink ref="AW45" r:id="rId323" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC"/>
+    <hyperlink ref="C46" r:id="rId324" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
+    <hyperlink ref="G46" r:id="rId325" tooltip="https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx"/>
+    <hyperlink ref="J46" r:id="rId326" tooltip="https://www.amazon.es/dp/B0DSC939TV?psc=1"/>
+    <hyperlink ref="K46" r:id="rId327" tooltip="https://m.media-amazon.com/images/I/41S5-Tk+PjL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId328" tooltip="https://www.amazon.es/dp/B0DSC939TV"/>
+    <hyperlink ref="M46" r:id="rId329" tooltip="https://www.amazon.es/b?node=2165709031"/>
+    <hyperlink ref="N46" r:id="rId330"/>
+    <hyperlink ref="C47" r:id="rId331" tooltip="https://www.amazon.es/dp/B0CWV3BTDZ"/>
+    <hyperlink ref="G47" r:id="rId332" tooltip="https://www.amazon.es/Kamanan/b/ref=bl_dp_s_web_66105826031?ie=UTF8&amp;node=66105826031&amp;field-lbr_brands_browse-bin=Kamanan"/>
+    <hyperlink ref="J47" r:id="rId333" tooltip="https://www.amazon.es/dp/B0CWV3BTDZ?psc=1"/>
+    <hyperlink ref="K47" r:id="rId334" tooltip="https://images-na.ssl-images-amazon.com/images/I/61MdLxg7mKL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId335" tooltip="https://www.amazon.es/dp/B0CWV3BTDZ"/>
+    <hyperlink ref="M47" r:id="rId336" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N47" r:id="rId337"/>
-    <hyperlink ref="C48" r:id="rId338" tooltip="https://www.amazon.es/dp/B0CWV3BTDZ"/>
-    <hyperlink ref="G48" r:id="rId339" tooltip="https://www.amazon.es/Kamanan/b/ref=bl_dp_s_web_66105826031?ie=UTF8&amp;node=66105826031&amp;field-lbr_brands_browse-bin=Kamanan"/>
-    <hyperlink ref="J48" r:id="rId340" tooltip="https://www.amazon.es/dp/B0CWV3BTDZ?psc=1"/>
-    <hyperlink ref="K48" r:id="rId341" tooltip="https://images-na.ssl-images-amazon.com/images/I/61MdLxg7mKL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId342" tooltip="https://www.amazon.es/dp/B0CWV3BTDZ"/>
-    <hyperlink ref="M48" r:id="rId343" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N48" r:id="rId344"/>
-    <hyperlink ref="AW48" r:id="rId345" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UMTMFY4BME13"/>
-    <hyperlink ref="C49" r:id="rId346" tooltip="https://www.amazon.es/dp/B0GL6L64YM"/>
-    <hyperlink ref="G49" r:id="rId347" tooltip="https://www.amazon.es/stores/WORKPRO/page/BDAC63AC-F4AC-4F79-BFBC-4C0D40DF1554?lp_asin=B0GL6L64YM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId348" tooltip="https://www.amazon.es/dp/B0GL6L64YM?psc=1"/>
-    <hyperlink ref="K49" r:id="rId349" tooltip="https://m.media-amazon.com/images/I/41P+iDWNq4L._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId350" tooltip="https://www.amazon.es/dp/B0GL6L64YM"/>
-    <hyperlink ref="M49" r:id="rId351" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N49" r:id="rId352"/>
-    <hyperlink ref="AW49" r:id="rId353" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC"/>
-    <hyperlink ref="C50" r:id="rId354" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
-    <hyperlink ref="G50" r:id="rId355" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kiseely"/>
-    <hyperlink ref="J50" r:id="rId356" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId357" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41jxwo0ip7L._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId358" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
-    <hyperlink ref="M50" r:id="rId359" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N50" r:id="rId360"/>
-    <hyperlink ref="AW50" r:id="rId361" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31A3I5NU1NCR2"/>
-    <hyperlink ref="C51" r:id="rId362" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
-    <hyperlink ref="G51" r:id="rId363" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J51" r:id="rId364" tooltip="https://www.amazon.es/dp/B0FNRQFHWC?psc=1"/>
-    <hyperlink ref="K51" r:id="rId365" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId366" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
+    <hyperlink ref="AW47" r:id="rId338" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UMTMFY4BME13"/>
+    <hyperlink ref="C48" r:id="rId339" tooltip="https://www.amazon.es/dp/B0GL6L64YM"/>
+    <hyperlink ref="G48" r:id="rId340" tooltip="https://www.amazon.es/stores/WORKPRO/page/BDAC63AC-F4AC-4F79-BFBC-4C0D40DF1554?lp_asin=B0GL6L64YM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId341" tooltip="https://www.amazon.es/dp/B0GL6L64YM?psc=1"/>
+    <hyperlink ref="K48" r:id="rId342" tooltip="https://m.media-amazon.com/images/I/41P+iDWNq4L._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId343" tooltip="https://www.amazon.es/dp/B0GL6L64YM"/>
+    <hyperlink ref="M48" r:id="rId344" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N48" r:id="rId345"/>
+    <hyperlink ref="AW48" r:id="rId346" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC"/>
+    <hyperlink ref="C49" r:id="rId347" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
+    <hyperlink ref="G49" r:id="rId348" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kiseely"/>
+    <hyperlink ref="J49" r:id="rId349" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ?psc=1"/>
+    <hyperlink ref="K49" r:id="rId350" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41jxwo0ip7L._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId351" tooltip="https://www.amazon.es/dp/B0HF7YZWZZ"/>
+    <hyperlink ref="M49" r:id="rId352" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N49" r:id="rId353"/>
+    <hyperlink ref="AW49" r:id="rId354" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31A3I5NU1NCR2"/>
+    <hyperlink ref="C50" r:id="rId355" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
+    <hyperlink ref="G50" r:id="rId356" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="J50" r:id="rId357" tooltip="https://www.amazon.es/dp/B0FNRQFHWC?psc=1"/>
+    <hyperlink ref="K50" r:id="rId358" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId359" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
   </hyperlinks>
-  <drawing r:id="rId367"/>
+  <drawing r:id="rId360"/>
 </worksheet>
 </file>
 
@@ -19217,7 +18944,7 @@
         <v>152.5250641175099</v>
       </c>
       <c r="G2" s="22">
-        <v>0.2341029419791496</v>
+        <v>0.23643880926130098</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19238,7 +18965,7 @@
         <v>185.56610044313146</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1478085257354948</v>
+        <v>0.14928335170893053</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19259,7 +18986,7 @@
         <v>88.1710502115137</v>
       </c>
       <c r="G4" s="22">
-        <v>0.29676327711369466</v>
+        <v>0.29972436604189634</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19269,18 +18996,18 @@
         </is>
       </c>
       <c r="B5" s="15">
-        <v>1349</v>
+        <v>1168</v>
       </c>
       <c r="C5" s="15">
-        <v>125156</v>
+        <v>121538</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="20">
-        <v>92.77687175685693</v>
+        <v>104.05650684931507</v>
       </c>
       <c r="G5" s="22">
-        <v>0.07363135200043666</v>
+        <v>0.06438809261300993</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19301,7 +19028,7 @@
         <v>44.505382775119614</v>
       </c>
       <c r="G6" s="22">
-        <v>0.09126139402871022</v>
+        <v>0.09217199558985667</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19322,7 +19049,7 @@
         <v>180.05626598465474</v>
       </c>
       <c r="G7" s="22">
-        <v>0.021341629823699578</v>
+        <v>0.02155457552370452</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19343,7 +19070,7 @@
         <v>176.15405405405406</v>
       </c>
       <c r="G8" s="22">
-        <v>0.020195404180994487</v>
+        <v>0.020396912899669238</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19364,7 +19091,7 @@
         <v>99.990990990991</v>
       </c>
       <c r="G9" s="22">
-        <v>0.024234485017193386</v>
+        <v>0.02447629547960309</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19385,7 +19112,7 @@
         <v>62.98974358974359</v>
       </c>
       <c r="G10" s="22">
-        <v>0.03193057147535615</v>
+        <v>0.03224917309812569</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19406,7 +19133,7 @@
         <v>65.98804780876495</v>
       </c>
       <c r="G11" s="22">
-        <v>0.013700125538998962</v>
+        <v>0.013836824696802646</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19427,7 +19154,7 @@
         <v>499.0</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0017466295507887124</v>
+        <v>0.0017640573318632856</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19448,7 +19175,7 @@
         <v>75.98159509202453</v>
       </c>
       <c r="G13" s="22">
-        <v>0.008896894274330004</v>
+        <v>0.00898566703417861</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19469,7 +19196,7 @@
         <v>163.33333333333334</v>
       </c>
       <c r="G14" s="22">
-        <v>0.003111183887342394</v>
+        <v>0.0031422271223814774</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19490,7 +19217,7 @@
         <v>112.9113924050633</v>
       </c>
       <c r="G15" s="22">
-        <v>0.004311991703509634</v>
+        <v>0.004355016538037486</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19511,7 +19238,7 @@
         <v>114.49230769230769</v>
       </c>
       <c r="G16" s="22">
-        <v>0.003547841275039572</v>
+        <v>0.003583241455347299</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19532,7 +19259,7 @@
         <v>85.1917808219178</v>
       </c>
       <c r="G17" s="22">
-        <v>0.00398449866273675</v>
+        <v>0.0040242557883131205</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19553,7 +19280,7 @@
         <v>67.9888888888889</v>
       </c>
       <c r="G18" s="22">
-        <v>0.004912395611593253</v>
+        <v>0.004961411245865491</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19574,7 +19301,7 @@
         <v>69.90123456790124</v>
       </c>
       <c r="G19" s="22">
-        <v>0.004421156050433929</v>
+        <v>0.004465270121278941</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19595,7 +19322,7 @@
         <v>100.0</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0026199443261830688</v>
+        <v>0.002646085997794928</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19616,7 +19343,7 @@
         <v>73.15217391304348</v>
       </c>
       <c r="G21" s="22">
-        <v>0.002510779979258774</v>
+        <v>0.002535832414553473</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19637,7 +19364,7 @@
         <v>140.0</v>
       </c>
       <c r="G22" s="22">
-        <v>0.0009824791223186507</v>
+        <v>0.000992282249173098</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19658,7 +19385,7 @@
         <v>140.0</v>
       </c>
       <c r="G23" s="22">
-        <v>0.0007641504284700616</v>
+        <v>0.0007717750826901874</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19679,7 +19406,7 @@
         <v>74.5</v>
       </c>
       <c r="G24" s="22">
-        <v>0.0010916434692429453</v>
+        <v>0.0011025358324145535</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19700,7 +19427,7 @@
         <v>47.0</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0015828830304022705</v>
+        <v>0.0015986769570011025</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19721,7 +19448,7 @@
         <v>90.0</v>
       </c>
       <c r="G26" s="22">
-        <v>0.0005458217346214726</v>
+        <v>0.0005512679162072767</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19804,18 +19531,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>14589</v>
+        <v>14408</v>
       </c>
       <c r="C2" s="15">
-        <v>1871376</v>
+        <v>1867758</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>128.2730824593872</v>
+        <v>129.6333981121599</v>
       </c>
       <c r="G2" s="22">
-        <v>0.7962993286392664</v>
+        <v>0.7942668136714444</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19836,7 +19563,7 @@
         <v>44.505382775119614</v>
       </c>
       <c r="G3" s="22">
-        <v>0.09126139402871022</v>
+        <v>0.09217199558985667</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19857,7 +19584,7 @@
         <v>105.89887640449439</v>
       </c>
       <c r="G4" s="22">
-        <v>0.02428906719065553</v>
+        <v>0.024531422271223815</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19878,7 +19605,7 @@
         <v>179.99122807017545</v>
       </c>
       <c r="G5" s="22">
-        <v>0.012444735549369576</v>
+        <v>0.01256890848952591</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19899,7 +19626,7 @@
         <v>62.98974358974359</v>
       </c>
       <c r="G6" s="22">
-        <v>0.03193057147535615</v>
+        <v>0.03224917309812569</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19920,7 +19647,7 @@
         <v>169.99295774647888</v>
       </c>
       <c r="G7" s="22">
-        <v>0.007750668631624912</v>
+        <v>0.00782800441014333</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19941,7 +19668,7 @@
         <v>65.98804780876495</v>
       </c>
       <c r="G8" s="22">
-        <v>0.013700125538998962</v>
+        <v>0.013836824696802646</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19962,7 +19689,7 @@
         <v>499.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0017466295507887124</v>
+        <v>0.0017640573318632856</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19983,7 +19710,7 @@
         <v>75.98159509202453</v>
       </c>
       <c r="G10" s="22">
-        <v>0.008896894274330004</v>
+        <v>0.00898566703417861</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20004,7 +19731,7 @@
         <v>73.56880733944953</v>
       </c>
       <c r="G11" s="22">
-        <v>0.005949456907374051</v>
+        <v>0.006008820286659317</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20025,7 +19752,7 @@
         <v>100.0</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0026199443261830688</v>
+        <v>0.002646085997794928</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20046,7 +19773,7 @@
         <v>140.0</v>
       </c>
       <c r="G13" s="22">
-        <v>0.0009824791223186507</v>
+        <v>0.000992282249173098</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20067,7 +19794,7 @@
         <v>47.0</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0015828830304022705</v>
+        <v>0.0015986769570011025</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20088,7 +19815,7 @@
         <v>90.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0005458217346214726</v>
+        <v>0.0005512679162072767</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
